--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ61"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135209812</v>
+        <v>137398664</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>92415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749818</v>
+        <v>750132</v>
       </c>
       <c r="R3" t="n">
-        <v>7298377</v>
+        <v>7298392</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +889,41 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209812</t>
+          <t>https://artportalen.se/Sighting/137398664</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135209826</v>
+        <v>137398682</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>92415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749873</v>
+        <v>749892</v>
       </c>
       <c r="R4" t="n">
-        <v>7298419</v>
+        <v>7298481</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -957,12 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,61 +1001,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209826</t>
+          <t>https://artportalen.se/Sighting/137398682</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135209829</v>
+        <v>137398698</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>92415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749929</v>
+        <v>749809</v>
       </c>
       <c r="R5" t="n">
-        <v>7298406</v>
+        <v>7298365</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1075,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Under murken låga precis i kanten av beståndet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,20 +1118,16 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209829</t>
+          <t>https://artportalen.se/Sighting/137398698</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135209843</v>
+        <v>135209812</v>
       </c>
       <c r="B6" t="n">
         <v>79107</v>
@@ -1139,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749843</v>
+        <v>749818</v>
       </c>
       <c r="R6" t="n">
-        <v>7298187</v>
+        <v>7298377</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,13 +1227,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209843</t>
+          <t>https://artportalen.se/Sighting/135209812</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135209845</v>
+        <v>135209826</v>
       </c>
       <c r="B7" t="n">
         <v>79107</v>
@@ -1241,14 +1264,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>749884</v>
+        <v>749873</v>
       </c>
       <c r="R7" t="n">
-        <v>7298115</v>
+        <v>7298419</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1310,13 +1333,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209845</t>
+          <t>https://artportalen.se/Sighting/135209826</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135209865</v>
+        <v>135209829</v>
       </c>
       <c r="B8" t="n">
         <v>79107</v>
@@ -1351,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750133</v>
+        <v>749929</v>
       </c>
       <c r="R8" t="n">
-        <v>7298382</v>
+        <v>7298406</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,13 +1439,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209865</t>
+          <t>https://artportalen.se/Sighting/135209829</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135209866</v>
+        <v>135209843</v>
       </c>
       <c r="B9" t="n">
         <v>79107</v>
@@ -1453,17 +1476,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750118</v>
+        <v>749843</v>
       </c>
       <c r="R9" t="n">
-        <v>7298394</v>
+        <v>7298187</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,16 +1545,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209866</t>
+          <t>https://artportalen.se/Sighting/135209843</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135209839</v>
+        <v>135209845</v>
       </c>
       <c r="B10" t="n">
-        <v>92321</v>
+        <v>79107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>749965</v>
+        <v>749884</v>
       </c>
       <c r="R10" t="n">
-        <v>7298287</v>
+        <v>7298115</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,16 +1651,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209839</t>
+          <t>https://artportalen.se/Sighting/135209845</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135209854</v>
+        <v>135209865</v>
       </c>
       <c r="B11" t="n">
-        <v>83292</v>
+        <v>79107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750085</v>
+        <v>750133</v>
       </c>
       <c r="R11" t="n">
-        <v>7298332</v>
+        <v>7298382</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,38 +1757,38 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209854</t>
+          <t>https://artportalen.se/Sighting/135209865</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135209810</v>
+        <v>135209866</v>
       </c>
       <c r="B12" t="n">
-        <v>101458</v>
+        <v>79107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1365</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,13 +1798,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750211</v>
+        <v>750118</v>
       </c>
       <c r="R12" t="n">
-        <v>7298618</v>
+        <v>7298394</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1840,16 +1863,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209810</t>
+          <t>https://artportalen.se/Sighting/135209866</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135209823</v>
+        <v>137398673</v>
       </c>
       <c r="B13" t="n">
-        <v>92103</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,37 +1880,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>749868</v>
+        <v>749929</v>
       </c>
       <c r="R13" t="n">
-        <v>7298423</v>
+        <v>7298340</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,12 +1934,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,23 +1972,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209823</t>
+          <t>https://artportalen.se/Sighting/137398673</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135209827</v>
+        <v>137398686</v>
       </c>
       <c r="B14" t="n">
-        <v>92103</v>
+        <v>79187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,21 +1992,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,13 +2016,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>749902</v>
+        <v>749883</v>
       </c>
       <c r="R14" t="n">
-        <v>7298417</v>
+        <v>7298461</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,12 +2046,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,23 +2084,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209827</t>
+          <t>https://artportalen.se/Sighting/137398686</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135209844</v>
+        <v>137398707</v>
       </c>
       <c r="B15" t="n">
-        <v>92103</v>
+        <v>79187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,21 +2104,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>749863</v>
+        <v>749835</v>
       </c>
       <c r="R15" t="n">
-        <v>7298165</v>
+        <v>7298330</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2123,17 +2158,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På silverlåga</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,61 +2196,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209844</t>
+          <t>https://artportalen.se/Sighting/137398707</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135209852</v>
+        <v>135209839</v>
       </c>
       <c r="B16" t="n">
-        <v>96115</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2387</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750082</v>
+        <v>749965</v>
       </c>
       <c r="R16" t="n">
-        <v>7298323</v>
+        <v>7298287</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2269,51 +2305,51 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209852</t>
+          <t>https://artportalen.se/Sighting/135209839</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135209819</v>
+        <v>135209854</v>
       </c>
       <c r="B17" t="n">
-        <v>97386</v>
+        <v>83292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>749895</v>
+        <v>750085</v>
       </c>
       <c r="R17" t="n">
-        <v>7298289</v>
+        <v>7298332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,38 +2411,38 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209819</t>
+          <t>https://artportalen.se/Sighting/135209854</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135209868</v>
+        <v>135209810</v>
       </c>
       <c r="B18" t="n">
-        <v>91972</v>
+        <v>101458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>1365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,13 +2452,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750122</v>
+        <v>750211</v>
       </c>
       <c r="R18" t="n">
-        <v>7298410</v>
+        <v>7298618</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,38 +2517,38 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209868</t>
+          <t>https://artportalen.se/Sighting/135209810</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135209814</v>
+        <v>137398702</v>
       </c>
       <c r="B19" t="n">
-        <v>93347</v>
+        <v>92348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>749891</v>
+        <v>749799</v>
       </c>
       <c r="R19" t="n">
-        <v>7298336</v>
+        <v>7298333</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2552,12 +2588,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2580,23 +2626,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209814</t>
+          <t>https://artportalen.se/Sighting/137398702</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135209820</v>
+        <v>137398676</v>
       </c>
       <c r="B20" t="n">
-        <v>93347</v>
+        <v>91173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,34 +2646,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>749955</v>
+        <v>749931</v>
       </c>
       <c r="R20" t="n">
-        <v>7298334</v>
+        <v>7298413</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2658,12 +2700,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,23 +2738,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209820</t>
+          <t>https://artportalen.se/Sighting/137398676</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135209821</v>
+        <v>137398694</v>
       </c>
       <c r="B21" t="n">
-        <v>93347</v>
+        <v>91173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,21 +2758,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,13 +2782,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>749926</v>
+        <v>749832</v>
       </c>
       <c r="R21" t="n">
-        <v>7298371</v>
+        <v>7298380</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2764,12 +2812,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2792,23 +2850,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209821</t>
+          <t>https://artportalen.se/Sighting/137398694</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135209822</v>
+        <v>137398711</v>
       </c>
       <c r="B22" t="n">
-        <v>93347</v>
+        <v>91173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,21 +2870,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,13 +2894,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>749902</v>
+        <v>749866</v>
       </c>
       <c r="R22" t="n">
-        <v>7298382</v>
+        <v>7298373</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2870,12 +2924,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,58 +2962,54 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209822</t>
+          <t>https://artportalen.se/Sighting/137398711</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135209828</v>
+        <v>137398704</v>
       </c>
       <c r="B23" t="n">
-        <v>93347</v>
+        <v>93485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>749895</v>
+        <v>749796</v>
       </c>
       <c r="R23" t="n">
-        <v>7298417</v>
+        <v>7298323</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2976,12 +3036,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,45 +3074,41 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209828</t>
+          <t>https://artportalen.se/Sighting/137398704</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135209842</v>
+        <v>137398724</v>
       </c>
       <c r="B24" t="n">
-        <v>93347</v>
+        <v>93485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,13 +3118,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>749888</v>
+        <v>749855</v>
       </c>
       <c r="R24" t="n">
-        <v>7298197</v>
+        <v>7298366</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3082,12 +3148,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3110,23 +3186,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209842</t>
+          <t>https://artportalen.se/Sighting/137398724</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135209847</v>
+        <v>135209823</v>
       </c>
       <c r="B25" t="n">
-        <v>93347</v>
+        <v>92103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,37 +3206,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>749884</v>
+        <v>749868</v>
       </c>
       <c r="R25" t="n">
-        <v>7298120</v>
+        <v>7298423</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3223,16 +3295,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209847</t>
+          <t>https://artportalen.se/Sighting/135209823</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135209848</v>
+        <v>135209827</v>
       </c>
       <c r="B26" t="n">
-        <v>93347</v>
+        <v>92103</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,37 +3312,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>749905</v>
+        <v>749902</v>
       </c>
       <c r="R26" t="n">
-        <v>7298128</v>
+        <v>7298417</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3329,16 +3401,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209848</t>
+          <t>https://artportalen.se/Sighting/135209827</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135209871</v>
+        <v>135209844</v>
       </c>
       <c r="B27" t="n">
-        <v>93347</v>
+        <v>92103</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,37 +3418,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750133</v>
+        <v>749863</v>
       </c>
       <c r="R27" t="n">
-        <v>7298449</v>
+        <v>7298165</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3406,6 +3478,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,16 +3512,16 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209871</t>
+          <t>https://artportalen.se/Sighting/135209844</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135209824</v>
+        <v>135209852</v>
       </c>
       <c r="B28" t="n">
-        <v>92013</v>
+        <v>96115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,21 +3529,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2387</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3553,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>749868</v>
+        <v>750082</v>
       </c>
       <c r="R28" t="n">
-        <v>7298423</v>
+        <v>7298323</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3541,16 +3618,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209824</t>
+          <t>https://artportalen.se/Sighting/135209852</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135209863</v>
+        <v>135209819</v>
       </c>
       <c r="B29" t="n">
-        <v>92013</v>
+        <v>97386</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3558,37 +3635,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750117</v>
+        <v>749895</v>
       </c>
       <c r="R29" t="n">
-        <v>7298359</v>
+        <v>7298289</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3647,38 +3724,38 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209863</t>
+          <t>https://artportalen.se/Sighting/135209819</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135209832</v>
+        <v>135209868</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>91972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3688,10 +3765,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750063</v>
+        <v>750122</v>
       </c>
       <c r="R30" t="n">
-        <v>7298466</v>
+        <v>7298410</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3753,54 +3830,54 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209832</t>
+          <t>https://artportalen.se/Sighting/135209868</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135209833</v>
+        <v>137398700</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>92091</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>750059</v>
+        <v>749802</v>
       </c>
       <c r="R31" t="n">
-        <v>7298397</v>
+        <v>7298343</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3824,12 +3901,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3852,45 +3939,41 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209833</t>
+          <t>https://artportalen.se/Sighting/137398700</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135209838</v>
+        <v>137398722</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>93461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,13 +3983,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750129</v>
+        <v>750120</v>
       </c>
       <c r="R32" t="n">
-        <v>7298358</v>
+        <v>7298422</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,12 +4013,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3958,45 +4051,41 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209838</t>
+          <t>https://artportalen.se/Sighting/137398722</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135209840</v>
+        <v>135209814</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>93347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4006,13 +4095,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>749885</v>
+        <v>749891</v>
       </c>
       <c r="R33" t="n">
-        <v>7298151</v>
+        <v>7298336</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4071,38 +4160,38 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209840</t>
+          <t>https://artportalen.se/Sighting/135209814</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135209857</v>
+        <v>135209820</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>93347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4112,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>750028</v>
+        <v>749955</v>
       </c>
       <c r="R34" t="n">
-        <v>7298282</v>
+        <v>7298334</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4177,16 +4266,16 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209857</t>
+          <t>https://artportalen.se/Sighting/135209820</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135209849</v>
+        <v>135209821</v>
       </c>
       <c r="B35" t="n">
-        <v>83428</v>
+        <v>93347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4194,21 +4283,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4218,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>750122</v>
+        <v>749926</v>
       </c>
       <c r="R35" t="n">
-        <v>7298331</v>
+        <v>7298371</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4283,16 +4372,16 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209849</t>
+          <t>https://artportalen.se/Sighting/135209821</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135209825</v>
+        <v>135209822</v>
       </c>
       <c r="B36" t="n">
-        <v>79198</v>
+        <v>93347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4300,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4324,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>749873</v>
+        <v>749902</v>
       </c>
       <c r="R36" t="n">
-        <v>7298425</v>
+        <v>7298382</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4389,16 +4478,16 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209825</t>
+          <t>https://artportalen.se/Sighting/135209822</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135209813</v>
+        <v>135209828</v>
       </c>
       <c r="B37" t="n">
-        <v>80060</v>
+        <v>93347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4406,37 +4495,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>749818</v>
+        <v>749895</v>
       </c>
       <c r="R37" t="n">
-        <v>7298374</v>
+        <v>7298417</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4495,16 +4584,16 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209813</t>
+          <t>https://artportalen.se/Sighting/135209828</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135209831</v>
+        <v>135209842</v>
       </c>
       <c r="B38" t="n">
-        <v>80060</v>
+        <v>93347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4512,34 +4601,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>750054</v>
+        <v>749888</v>
       </c>
       <c r="R38" t="n">
-        <v>7298481</v>
+        <v>7298197</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4601,16 +4690,16 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209831</t>
+          <t>https://artportalen.se/Sighting/135209842</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135209846</v>
+        <v>135209847</v>
       </c>
       <c r="B39" t="n">
-        <v>80060</v>
+        <v>93347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,21 +4707,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4642,13 +4731,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>749885</v>
+        <v>749884</v>
       </c>
       <c r="R39" t="n">
-        <v>7298116</v>
+        <v>7298120</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4707,16 +4796,16 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209846</t>
+          <t>https://artportalen.se/Sighting/135209847</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135209867</v>
+        <v>135209848</v>
       </c>
       <c r="B40" t="n">
-        <v>80060</v>
+        <v>93347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4724,37 +4813,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>750118</v>
+        <v>749905</v>
       </c>
       <c r="R40" t="n">
-        <v>7298402</v>
+        <v>7298128</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4813,38 +4902,38 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209867</t>
+          <t>https://artportalen.se/Sighting/135209848</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135209851</v>
+        <v>135209871</v>
       </c>
       <c r="B41" t="n">
-        <v>80450</v>
+        <v>93347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4854,13 +4943,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>750092</v>
+        <v>750133</v>
       </c>
       <c r="R41" t="n">
-        <v>7298316</v>
+        <v>7298449</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4919,16 +5008,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209851</t>
+          <t>https://artportalen.se/Sighting/135209871</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135209864</v>
+        <v>137398680</v>
       </c>
       <c r="B42" t="n">
-        <v>78445</v>
+        <v>93469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4936,21 +5025,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +5049,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>750122</v>
+        <v>749917</v>
       </c>
       <c r="R42" t="n">
-        <v>7298377</v>
+        <v>7298448</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -4990,12 +5079,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5018,23 +5117,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209864</t>
+          <t>https://artportalen.se/Sighting/137398680</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135209811</v>
+        <v>137398692</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>93469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5042,39 +5137,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>750075</v>
+        <v>749843</v>
       </c>
       <c r="R43" t="n">
-        <v>7298357</v>
+        <v>7298382</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5101,17 +5191,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,66 +5229,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209811</t>
+          <t>https://artportalen.se/Sighting/137398692</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135209815</v>
+        <v>137398666</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>93473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>749879</v>
+        <v>750112</v>
       </c>
       <c r="R44" t="n">
-        <v>7298305</v>
+        <v>7298377</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5217,17 +5303,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5250,66 +5341,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209815</t>
+          <t>https://artportalen.se/Sighting/137398666</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135209816</v>
+        <v>137398690</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>93473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>749879</v>
+        <v>749851</v>
       </c>
       <c r="R45" t="n">
-        <v>7298274</v>
+        <v>7298405</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5333,17 +5415,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,66 +5453,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209816</t>
+          <t>https://artportalen.se/Sighting/137398690</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135209817</v>
+        <v>137398713</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>93473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>749874</v>
+        <v>749892</v>
       </c>
       <c r="R46" t="n">
-        <v>7298266</v>
+        <v>7298384</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5449,17 +5527,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5482,23 +5565,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209817</t>
+          <t>https://artportalen.se/Sighting/137398713</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135209818</v>
+        <v>137398678</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>90761</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5506,42 +5585,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>749913</v>
+        <v>749930</v>
       </c>
       <c r="R47" t="n">
-        <v>7298270</v>
+        <v>7298425</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5565,17 +5639,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5598,63 +5677,54 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209818</t>
+          <t>https://artportalen.se/Sighting/137398678</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135209850</v>
+        <v>135209824</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>92013</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>750113</v>
+        <v>749868</v>
       </c>
       <c r="R48" t="n">
-        <v>7298320</v>
+        <v>7298423</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5716,63 +5786,54 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209850</t>
+          <t>https://artportalen.se/Sighting/135209824</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135209835</v>
+        <v>135209863</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>92013</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>750247</v>
+        <v>750117</v>
       </c>
       <c r="R49" t="n">
-        <v>7298561</v>
+        <v>7298359</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5831,60 +5892,51 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209835</t>
+          <t>https://artportalen.se/Sighting/135209863</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135209837</v>
+        <v>137398667</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>92132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>750231</v>
+        <v>750046</v>
       </c>
       <c r="R50" t="n">
-        <v>7298596</v>
+        <v>7298312</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5911,12 +5963,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,45 +6001,41 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209837</t>
+          <t>https://artportalen.se/Sighting/137398667</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135209853</v>
+        <v>137398688</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>93495</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,13 +6045,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>750081</v>
+        <v>749911</v>
       </c>
       <c r="R51" t="n">
-        <v>7298328</v>
+        <v>7298398</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6017,12 +6075,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6045,70 +6113,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209853</t>
+          <t>https://artportalen.se/Sighting/137398688</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135209856</v>
+        <v>137398709</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>93495</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>750054</v>
+        <v>749868</v>
       </c>
       <c r="R52" t="n">
-        <v>7298313</v>
+        <v>7298356</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6132,12 +6187,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,70 +6225,57 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209856</t>
+          <t>https://artportalen.se/Sighting/137398709</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135209858</v>
+        <v>137398696</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>91523</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>750024</v>
+        <v>749833</v>
       </c>
       <c r="R53" t="n">
-        <v>7298300</v>
+        <v>7298367</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,12 +6299,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6275,23 +6337,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209858</t>
+          <t>https://artportalen.se/Sighting/137398696</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135209861</v>
+        <v>137398710</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>93453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6299,43 +6357,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>750071</v>
+        <v>749866</v>
       </c>
       <c r="R54" t="n">
-        <v>7298359</v>
+        <v>7298373</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6362,12 +6411,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6390,23 +6449,19 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Stenvalls trä AB - Second opinion 2026</t>
-        </is>
-      </c>
+      <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209861</t>
+          <t>https://artportalen.se/Sighting/137398710</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135209862</v>
+        <v>135209832</v>
       </c>
       <c r="B55" t="n">
-        <v>99276</v>
+        <v>79441</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6414,46 +6469,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>750070</v>
+        <v>750063</v>
       </c>
       <c r="R55" t="n">
-        <v>7298363</v>
+        <v>7298466</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6512,38 +6558,38 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209862</t>
+          <t>https://artportalen.se/Sighting/135209832</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135209836</v>
+        <v>135209833</v>
       </c>
       <c r="B56" t="n">
-        <v>106413</v>
+        <v>79441</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6553,10 +6599,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>750233</v>
+        <v>750059</v>
       </c>
       <c r="R56" t="n">
-        <v>7298598</v>
+        <v>7298397</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6618,38 +6664,38 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209836</t>
+          <t>https://artportalen.se/Sighting/135209833</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135209860</v>
+        <v>135209838</v>
       </c>
       <c r="B57" t="n">
-        <v>106398</v>
+        <v>79441</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6659,13 +6705,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>750067</v>
+        <v>750129</v>
       </c>
       <c r="R57" t="n">
-        <v>7298333</v>
+        <v>7298358</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6724,51 +6770,51 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209860</t>
+          <t>https://artportalen.se/Sighting/135209838</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135209870</v>
+        <v>135209840</v>
       </c>
       <c r="B58" t="n">
-        <v>79199</v>
+        <v>79441</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>750113</v>
+        <v>749885</v>
       </c>
       <c r="R58" t="n">
-        <v>7298446</v>
+        <v>7298151</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6830,54 +6876,54 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209870</t>
+          <t>https://artportalen.se/Sighting/135209840</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135209830</v>
+        <v>135209857</v>
       </c>
       <c r="B59" t="n">
-        <v>80031</v>
+        <v>79441</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Furumyran, Nb</t>
+          <t>Rudtjärnarna, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>749930</v>
+        <v>750028</v>
       </c>
       <c r="R59" t="n">
-        <v>7298408</v>
+        <v>7298282</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6936,16 +6982,16 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209830</t>
+          <t>https://artportalen.se/Sighting/135209857</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135209841</v>
+        <v>135209849</v>
       </c>
       <c r="B60" t="n">
-        <v>80031</v>
+        <v>83428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6953,37 +6999,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rudtjärnarna, Nb</t>
+          <t>Furumyran, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>749875</v>
+        <v>750122</v>
       </c>
       <c r="R60" t="n">
-        <v>7298152</v>
+        <v>7298331</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7042,16 +7088,16 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135209841</t>
+          <t>https://artportalen.se/Sighting/135209849</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135209869</v>
+        <v>135209825</v>
       </c>
       <c r="B61" t="n">
-        <v>80031</v>
+        <v>79198</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7059,21 +7105,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7083,13 +7129,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>750122</v>
+        <v>749873</v>
       </c>
       <c r="R61" t="n">
-        <v>7298419</v>
+        <v>7298425</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7148,7 +7194,3326 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135209825</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137398671</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79278</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>749930</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7298341</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137398671</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135209813</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>749818</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7298374</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209813</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135209831</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>750054</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7298481</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209831</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135209846</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>749885</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7298116</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209846</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135209867</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>750118</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7298402</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209867</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137398705</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>749790</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7298323</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137398705</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135209851</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80450</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>750092</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7298316</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209851</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137398684</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80530</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>749902</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7298486</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137398684</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135209864</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>750122</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7298377</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209864</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135209811</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>750075</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7298357</v>
+      </c>
+      <c r="S71" t="n">
+        <v>4</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209811</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135209815</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>749879</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7298305</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209815</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135209816</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>749879</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7298274</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209816</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135209817</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>749874</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7298266</v>
+      </c>
+      <c r="S74" t="n">
+        <v>4</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209817</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135209818</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>749913</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7298270</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209818</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135209850</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>750113</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7298320</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209850</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135209835</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>750247</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7298561</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209835</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135209837</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>750231</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7298596</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209837</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135209853</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>750081</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7298328</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209853</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135209856</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>750054</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7298313</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209856</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135209858</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>750024</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7298300</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209858</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135209861</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>750071</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7298359</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209861</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135209862</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>750070</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7298363</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209862</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135209836</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>750233</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7298598</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209836</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135209860</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106398</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>750067</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7298333</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209860</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135209870</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>750113</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7298446</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209870</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135209830</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>749930</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7298408</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209830</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135209841</v>
+      </c>
+      <c r="B88" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Rudtjärnarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>749875</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7298152</v>
+      </c>
+      <c r="S88" t="n">
+        <v>3</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209841</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135209869</v>
+      </c>
+      <c r="B89" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>750122</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7298419</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Stenvalls trä AB - Second opinion 2026</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135209869</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>137398669</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>749960</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7298359</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137398669</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>137398675</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Furumyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>749944</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7298401</v>
+      </c>
+      <c r="S91" t="n">
+        <v>4</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137398675</t>
         </is>
       </c>
     </row>
@@ -7214,6 +10579,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137398664</v>
       </c>
       <c r="B3" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137398682</v>
       </c>
       <c r="B4" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137398698</v>
       </c>
       <c r="B5" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137398673</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>137398686</v>
       </c>
       <c r="B14" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137398707</v>
       </c>
       <c r="B15" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>137398702</v>
       </c>
       <c r="B19" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>137398676</v>
       </c>
       <c r="B20" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137398694</v>
       </c>
       <c r="B21" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137398711</v>
       </c>
       <c r="B22" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137398704</v>
       </c>
       <c r="B23" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137398724</v>
       </c>
       <c r="B24" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>137398700</v>
       </c>
       <c r="B31" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>137398722</v>
       </c>
       <c r="B32" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>137398680</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>137398692</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>137398666</v>
       </c>
       <c r="B44" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>137398690</v>
       </c>
       <c r="B45" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>137398713</v>
       </c>
       <c r="B46" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137398678</v>
       </c>
       <c r="B47" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>137398667</v>
       </c>
       <c r="B50" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137398688</v>
       </c>
       <c r="B51" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>137398709</v>
       </c>
       <c r="B52" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>137398696</v>
       </c>
       <c r="B53" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>137398710</v>
       </c>
       <c r="B54" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>137398671</v>
       </c>
       <c r="B62" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137398705</v>
       </c>
       <c r="B67" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>137398684</v>
       </c>
       <c r="B69" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>137398669</v>
       </c>
       <c r="B90" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137398675</v>
       </c>
       <c r="B91" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137398664</v>
       </c>
       <c r="B3" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137398682</v>
       </c>
       <c r="B4" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137398698</v>
       </c>
       <c r="B5" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137398673</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>137398686</v>
       </c>
       <c r="B14" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137398707</v>
       </c>
       <c r="B15" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>137398702</v>
       </c>
       <c r="B19" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>137398676</v>
       </c>
       <c r="B20" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137398694</v>
       </c>
       <c r="B21" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137398711</v>
       </c>
       <c r="B22" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137398704</v>
       </c>
       <c r="B23" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137398724</v>
       </c>
       <c r="B24" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>137398700</v>
       </c>
       <c r="B31" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>137398722</v>
       </c>
       <c r="B32" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>137398680</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>137398692</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>137398666</v>
       </c>
       <c r="B44" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>137398690</v>
       </c>
       <c r="B45" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>137398713</v>
       </c>
       <c r="B46" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137398678</v>
       </c>
       <c r="B47" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>137398667</v>
       </c>
       <c r="B50" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137398688</v>
       </c>
       <c r="B51" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>137398709</v>
       </c>
       <c r="B52" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>137398696</v>
       </c>
       <c r="B53" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>137398710</v>
       </c>
       <c r="B54" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>137398671</v>
       </c>
       <c r="B62" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137398705</v>
       </c>
       <c r="B67" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>137398684</v>
       </c>
       <c r="B69" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>137398669</v>
       </c>
       <c r="B90" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137398675</v>
       </c>
       <c r="B91" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137398664</v>
       </c>
       <c r="B3" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137398682</v>
       </c>
       <c r="B4" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137398698</v>
       </c>
       <c r="B5" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137398673</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>137398686</v>
       </c>
       <c r="B14" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137398707</v>
       </c>
       <c r="B15" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>137398702</v>
       </c>
       <c r="B19" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>137398676</v>
       </c>
       <c r="B20" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137398694</v>
       </c>
       <c r="B21" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137398711</v>
       </c>
       <c r="B22" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137398704</v>
       </c>
       <c r="B23" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137398724</v>
       </c>
       <c r="B24" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>137398700</v>
       </c>
       <c r="B31" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>137398722</v>
       </c>
       <c r="B32" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>137398680</v>
       </c>
       <c r="B42" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>137398692</v>
       </c>
       <c r="B43" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>137398666</v>
       </c>
       <c r="B44" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>137398690</v>
       </c>
       <c r="B45" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>137398713</v>
       </c>
       <c r="B46" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137398678</v>
       </c>
       <c r="B47" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>137398667</v>
       </c>
       <c r="B50" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137398688</v>
       </c>
       <c r="B51" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>137398709</v>
       </c>
       <c r="B52" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>137398696</v>
       </c>
       <c r="B53" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>137398710</v>
       </c>
       <c r="B54" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>137398671</v>
       </c>
       <c r="B62" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137398705</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>137398684</v>
       </c>
       <c r="B69" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>137398669</v>
       </c>
       <c r="B90" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137398675</v>
       </c>
       <c r="B91" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137398664</v>
       </c>
       <c r="B3" t="n">
-        <v>92431</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137398682</v>
       </c>
       <c r="B4" t="n">
-        <v>92431</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137398698</v>
       </c>
       <c r="B5" t="n">
-        <v>92431</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137398673</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>137398686</v>
       </c>
       <c r="B14" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137398707</v>
       </c>
       <c r="B15" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>137398702</v>
       </c>
       <c r="B19" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>137398676</v>
       </c>
       <c r="B20" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137398694</v>
       </c>
       <c r="B21" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137398711</v>
       </c>
       <c r="B22" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137398704</v>
       </c>
       <c r="B23" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137398724</v>
       </c>
       <c r="B24" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>137398700</v>
       </c>
       <c r="B31" t="n">
-        <v>92107</v>
+        <v>92111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>137398722</v>
       </c>
       <c r="B32" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>137398680</v>
       </c>
       <c r="B42" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>137398692</v>
       </c>
       <c r="B43" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>137398666</v>
       </c>
       <c r="B44" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>137398690</v>
       </c>
       <c r="B45" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>137398713</v>
       </c>
       <c r="B46" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137398678</v>
       </c>
       <c r="B47" t="n">
-        <v>90776</v>
+        <v>90780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>137398667</v>
       </c>
       <c r="B50" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137398688</v>
       </c>
       <c r="B51" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>137398709</v>
       </c>
       <c r="B52" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>137398696</v>
       </c>
       <c r="B53" t="n">
-        <v>91539</v>
+        <v>91543</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>137398710</v>
       </c>
       <c r="B54" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>137398671</v>
       </c>
       <c r="B62" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137398705</v>
       </c>
       <c r="B67" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>137398684</v>
       </c>
       <c r="B69" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>137398669</v>
       </c>
       <c r="B90" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137398675</v>
       </c>
       <c r="B91" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
